--- a/processed_ruby_restored_xlsx/sc201_共有１：花火大会の朝.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc201_共有１：花火大会の朝.ss.xlsx
@@ -530,8 +530,8 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>As I called everyone like always, Nono-chan came over,
-even more bubbly than usual.</t>
+          <t>As I called everyone like always, Nono-chan came
+over, even more bubbly than usual.</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -730,8 +730,8 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan, who had come along with Nono-chan, cut
-in with a slightly embarrassed laugh.</t>
+          <t>Rurichiyo-chan, who had come along with Nono-chan,
+cut in with a slightly embarrassed laugh.</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1051,7 +1051,8 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Good morning！ Do you know what day it is today！？」</t>
+          <t>「Ah！ Good morning！ Do you know what day it is
+today！？」</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1205,7 +1206,8 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>「Well, for now everyone's here. So then, let's eat...」</t>
+          <t>「Well, for now everyone's here. So then, let's
+eat...」</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1235,10 +1237,10 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>「What kind of fireworks do you think we'll see... I've
-heard of fireworks that make pictures or letters, but
-are there fireworks that spin like a merry-go-round
-too!？」</t>
+          <t>「What kind of fireworks do you think we'll see...
+I've heard of fireworks that make pictures or
+letters, but are there fireworks that spin like a
+merry-go-round too!？」</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1423,8 +1425,8 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>The mood couldn't be brighter, but it didn't seem like
-they'd get any substantive information.</t>
+          <t>The mood couldn't be brighter, but it didn't seem
+like they'd get any substantive information.</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1531,7 +1533,8 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>Yet, my passion for fireworks shows no sign of fading.</t>
+          <t>Yet, my passion for fireworks shows no sign of
+fading.</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1622,8 +1625,8 @@
       <c r="B76" s="1" t="inlineStr">
         <is>
           <t>I figure fireworks festivals are held all over Japan,
-but when you ask which ones..., you surprisingly don't
-know.</t>
+but when you ask which ones..., you surprisingly
+don't know.</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1853,8 +1856,8 @@
       <c r="B91" s="1" t="inlineStr">
         <is>
           <t>Someone who grew up in the countryside, so Tokyo is
-something I only see on TV and it only has a glamorous
-image to me.</t>
+something I only see on TV and it only has a
+glamorous image to me.</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1901,8 +1904,8 @@
       <c r="B94" s="1" t="inlineStr">
         <is>
           <t>「Hmm... Tokyo has taller buildings and more
-streetlights, so wouldn’t the fireworks look better in
-a place with less of that...？」</t>
+streetlights, so wouldn’t the fireworks look better
+in a place with less of that...？」</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2120,8 +2123,8 @@
       <c r="B108" s="1" t="inlineStr">
         <is>
           <t>「Ah... it looks like there's a fireworks competition.
-It seems like the craftsmen bring their best fireworks
-to show off.」</t>
+It seems like the craftsmen bring their best
+fireworks to show off.」</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2783,8 +2786,8 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Maybe because she got lured by Miru-chan, Rin-chan ran
-over with her sleeves spread wide.</t>
+          <t>Maybe because she got lured by Miru-chan, Rin-chan
+ran over with her sleeves spread wide.</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3177,8 +3180,8 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>As Rurichiyo-chan praised me and I gave an embarrassed
-smile, she tugged at my sleeve a little.</t>
+          <t>As Rurichiyo-chan praised me and I gave an
+embarrassed smile, she tugged at my sleeve a little.</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3503,7 +3506,8 @@
       <c r="B198" s="1" t="inlineStr">
         <is>
           <t>When Miru-chan and Rurichiyo-chan spoke in turn,
-Nono-chan nodded her head with a thoughtful 'hmm-hmm.'</t>
+Nono-chan nodded her head with a thoughtful
+'hmm-hmm.'</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3800,8 +3804,8 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>「Rin, if you buy too much like that, you’ll run out of
-allowance again, y’know？」</t>
+          <t>「Rin, if you buy too much like that, you’ll run out
+of allowance again, y’know？」</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3937,8 +3941,8 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>I avoided making a statement because whether it starts
-depends on the pyrotechnician’s preparations.</t>
+          <t>I avoided making a statement because whether it
+starts depends on the pyrotechnician’s preparations.</t>
         </is>
       </c>
       <c r="C226" t="n">

--- a/processed_ruby_restored_xlsx/sc201_共有１：花火大会の朝.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc201_共有１：花火大会の朝.ss.xlsx
@@ -621,9 +621,9 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>「That's right！ Fireworks！ This is the very symbol of
+          <t>That's right！ Fireworks！ This is the very symbol of
 Japan's seasonal traditions！ I just couldn't wait any
-longer~！」</t>
+longer~！</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu... well, I suppose...」</t>
+          <t>Ufufu... well, I suppose...</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>「Now, now, both of you—calm down a bit…」</t>
+          <t>Now, now, both of you—calm down a bit…</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1656,8 +1656,8 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>「If we're talking famous, maybe the Sumida River —
-what do you think？」</t>
+          <t>If we're talking famous, maybe the Sumida River —
+what do you think？</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>「Really？ Isn't Tokyo cleaner？」</t>
+          <t>Really？ Isn't Tokyo cleaner？</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2217,7 +2217,7 @@
       <c r="B114" s="1" t="inlineStr">
         <is>
           <t>For now, there's an amazing fireworks festival...
-knowing that, she's probably satisfied for now.</t>
+knowing that, they're probably satisfied for now.</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>「…uh, shall we go ahead and eat now？」</t>
+          <t>…uh, shall we go ahead and eat now？</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>「Hehe~！ How is it？ How is it？ I'm wearing a yukata！」</t>
+          <t>Hehe~！ How is it？ How is it？ I'm wearing a yukata！</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3043,8 +3043,8 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>You could say she looks like a pro just from the way
-she walks.</t>
+          <t>You could say they look like a pro just from the way
+they walk.</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei's wearing a yukata too！」</t>
+          <t>Janitor-sensei's wearing a yukata too！</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3180,8 +3180,8 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>As Rurichiyo-chan praised me and I gave an
-embarrassed smile, she tugged at my sleeve a little.</t>
+          <t>As Rurichiyo-chan praised him and he gave an
+embarrassed smile, she tugged at his sleeve a little.</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>「Ooooohhh！？」</t>
+          <t>Ooooohhh！？</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>「Ha— it's starting！ Everyyone！」</t>
+          <t>Ha— it's starting！ Everyyone！</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>「Waaah… S-s-so it is?！」</t>
+          <t>Waaah… S-s-so it is?！</t>
         </is>
       </c>
       <c r="C254" t="n">
